--- a/artfynd/A 54802-2021 artfynd.xlsx
+++ b/artfynd/A 54802-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1329,6 +1329,123 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125120155</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Övre Galvattssjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>490294</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6932265</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rätan</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>04:56</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>04:56</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca 100 plantor.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tobias Nykänen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tobias Nykänen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54802-2021 artfynd.xlsx
+++ b/artfynd/A 54802-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1329,123 +1329,6 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>125120155</v>
-      </c>
-      <c r="B8" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Övre Galvattssjön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>490294</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6932265</v>
-      </c>
-      <c r="S8" t="n">
-        <v>15</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Rätan</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>04:56</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-05-16</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>04:56</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ca 100 plantor.</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Tobias Nykänen</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Tobias Nykänen</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54802-2021 artfynd.xlsx
+++ b/artfynd/A 54802-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,43 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114901091</v>
+        <v>114901111</v>
       </c>
       <c r="B2" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -757,17 +751,13 @@
           <t>2024-02-27</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114901111</v>
+        <v>114901044</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,26 +787,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>490422</v>
+        <v>490302</v>
       </c>
       <c r="R3" t="n">
-        <v>6932196</v>
+        <v>6932274</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -867,13 +853,17 @@
           <t>2024-02-27</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -892,15 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114901044</v>
+        <v>114901060</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,10 +921,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490302</v>
+        <v>490366</v>
       </c>
       <c r="R4" t="n">
-        <v>6932274</v>
+        <v>6932209</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1003,15 +988,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114901164</v>
+        <v>114901073</v>
       </c>
       <c r="B5" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,26 +999,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1046,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490501</v>
+        <v>490431</v>
       </c>
       <c r="R5" t="n">
-        <v>6932143</v>
+        <v>6932189</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,13 +1065,17 @@
           <t>2024-02-27</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1109,15 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114901060</v>
+        <v>114901091</v>
       </c>
       <c r="B6" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490366</v>
+        <v>490422</v>
       </c>
       <c r="R6" t="n">
-        <v>6932209</v>
+        <v>6932196</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,117 +1197,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>114901073</v>
-      </c>
-      <c r="B7" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Övre Galvattsjön , Jmt</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>490431</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6932189</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Rätan</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2024-02-27</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2024-02-27</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Marielle Löthman</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Marielle Löthman</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54802-2021 artfynd.xlsx
+++ b/artfynd/A 54802-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114901111</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114901044</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114901060</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114901073</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,8 +1222,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114901091</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>